--- a/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F8214A-20F4-416E-A2BF-6E36E4CEA8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C85A47-0E1B-41A2-8FA9-9C6B9EB52731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="55">
   <si>
     <t>Result</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Thu Sep 10 21:01:49 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Sep 10 21:03:31 IST 2026</t>
   </si>
   <si>
@@ -208,20 +205,52 @@
     <t>03</t>
   </si>
   <si>
-    <t>Tue Sep 15 20:58:29 IST 2026</t>
-  </si>
-  <si>
     <t>2223520443560010</t>
   </si>
   <si>
     <t>Tue Sep 15 21:08:53 IST 2026</t>
+  </si>
+  <si>
+    <t>RoutingNo</t>
+  </si>
+  <si>
+    <t>AccountNo</t>
+  </si>
+  <si>
+    <t>ConfirmAccNo</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>AccType</t>
+  </si>
+  <si>
+    <t>256072691</t>
+  </si>
+  <si>
+    <t>65987541</t>
+  </si>
+  <si>
+    <t>1234567</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>Wed Sep 16 22:38:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Savings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -263,7 +292,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,6 +308,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,7 +346,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -354,6 +389,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -693,13 +731,13 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
-    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="25.7265625" style="7" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -769,25 +807,25 @@
   <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="8.08984375"/>
-    <col min="2" max="2" customWidth="true" style="4" width="23.90625"/>
-    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
-    <col min="4" max="4" style="4" width="8.7265625"/>
-    <col min="5" max="5" customWidth="true" style="11" width="18.36328125"/>
-    <col min="6" max="6" customWidth="true" style="4" width="7.36328125"/>
-    <col min="7" max="7" style="4" width="8.7265625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="7.81640625"/>
-    <col min="9" max="9" customWidth="true" style="4" width="6.54296875"/>
-    <col min="10" max="10" customWidth="true" style="4" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="4" width="8.54296875"/>
-    <col min="12" max="12" customWidth="true" style="4" width="5.7265625"/>
-    <col min="13" max="13" customWidth="true" style="4" width="8.453125"/>
-    <col min="14" max="14" customWidth="true" style="4" width="9.6328125"/>
-    <col min="15" max="15" customWidth="true" style="4" width="5.0"/>
-    <col min="16" max="16" customWidth="true" style="4" width="6.1796875"/>
-    <col min="17" max="17" customWidth="true" style="4" width="5.08984375"/>
-    <col min="18" max="18" customWidth="true" style="4" width="5.7265625"/>
-    <col min="19" max="16384" style="4" width="8.7265625"/>
+    <col min="1" max="1" width="8.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.90625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="4"/>
+    <col min="5" max="5" width="18.36328125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="4"/>
+    <col min="8" max="8" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.54296875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.54296875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.453125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="5" style="4" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="5.08984375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="5.7265625" style="4" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
@@ -804,73 +842,73 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
@@ -878,13 +916,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="4">
         <v>12</v>
@@ -899,10 +937,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>37</v>
       </c>
       <c r="G3" s="4">
         <v>2028</v>
@@ -922,25 +960,25 @@
   <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="8.08984375"/>
-    <col min="2" max="2" customWidth="true" style="4" width="23.90625"/>
-    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
-    <col min="4" max="4" style="4" width="8.7265625"/>
-    <col min="5" max="5" customWidth="true" style="11" width="18.36328125"/>
-    <col min="6" max="6" customWidth="true" style="4" width="7.36328125"/>
-    <col min="7" max="7" style="4" width="8.7265625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="7.81640625"/>
-    <col min="9" max="9" customWidth="true" style="4" width="6.54296875"/>
-    <col min="10" max="10" customWidth="true" style="4" width="9.0"/>
-    <col min="11" max="11" customWidth="true" style="4" width="8.54296875"/>
-    <col min="12" max="12" customWidth="true" style="4" width="5.7265625"/>
-    <col min="13" max="13" customWidth="true" style="4" width="8.453125"/>
-    <col min="14" max="14" customWidth="true" style="4" width="9.6328125"/>
-    <col min="15" max="15" customWidth="true" style="4" width="5.0"/>
-    <col min="16" max="16" customWidth="true" style="4" width="6.1796875"/>
-    <col min="17" max="17" customWidth="true" style="4" width="5.08984375"/>
-    <col min="18" max="18" customWidth="true" style="4" width="5.7265625"/>
-    <col min="19" max="16384" style="4" width="8.7265625"/>
+    <col min="1" max="1" width="8.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.90625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="4"/>
+    <col min="5" max="5" width="18.36328125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="4"/>
+    <col min="8" max="8" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.54296875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9" style="4" customWidth="1"/>
+    <col min="11" max="11" width="8.54296875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.453125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="5" style="4" customWidth="1"/>
+    <col min="16" max="16" width="6.1796875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="5.08984375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="5.7265625" style="4" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
@@ -957,73 +995,73 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="25" x14ac:dyDescent="0.25">
@@ -1031,16 +1069,16 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4">
         <v>2030</v>
@@ -1052,10 +1090,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E3" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" s="4">
         <v>2028</v>
@@ -1072,19 +1110,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7982227C-0283-439A-A797-C382419F435A}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
-    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.81640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="7.54296875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.453125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="9.6328125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="5" style="4" customWidth="1"/>
+    <col min="17" max="17" width="6.1796875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="5.08984375" style="4" customWidth="1"/>
+    <col min="19" max="19" width="5.7265625" style="4" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1098,52 +1149,125 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
+      <c r="B2" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1152,19 +1276,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5751A425-4B52-4060-AB3E-0797817D9EF5}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
-    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.81640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="7.54296875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="5.7265625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.453125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="9.6328125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="5" style="4" customWidth="1"/>
+    <col min="17" max="17" width="6.1796875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="5.08984375" style="4" customWidth="1"/>
+    <col min="19" max="19" width="5.7265625" style="4" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1178,52 +1315,110 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="5"/>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1235,13 +1430,13 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
-    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="25.7265625" style="7" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1269,7 +1464,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>

--- a/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C85A47-0E1B-41A2-8FA9-9C6B9EB52731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193BA79-F68E-43BD-80F9-FA697F96726A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="63">
   <si>
     <t>Result</t>
   </si>
@@ -246,11 +246,36 @@
   <si>
     <t>Savings</t>
   </si>
+  <si>
+    <t>95125489</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thu Sep 17 13:13:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 13:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 13:25:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 13:26:31 IST 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -346,7 +371,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -392,6 +417,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -731,13 +759,13 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.7265625" style="7" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -807,25 +835,25 @@
   <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.08984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.90625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="4"/>
-    <col min="5" max="5" width="18.36328125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="4"/>
-    <col min="8" max="8" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.54296875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.54296875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="5.7265625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="8.453125" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.6328125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="5" style="4" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="5.7265625" style="4" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="8.08984375"/>
+    <col min="2" max="2" customWidth="true" style="4" width="23.90625"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" style="4" width="8.7265625"/>
+    <col min="5" max="5" customWidth="true" style="11" width="18.36328125"/>
+    <col min="6" max="6" customWidth="true" style="4" width="7.36328125"/>
+    <col min="7" max="7" style="4" width="8.7265625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="7.81640625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="6.54296875"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="4" width="8.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="5.7265625"/>
+    <col min="13" max="13" customWidth="true" style="4" width="8.453125"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.6328125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="5.0"/>
+    <col min="16" max="16" customWidth="true" style="4" width="6.1796875"/>
+    <col min="17" max="17" customWidth="true" style="4" width="5.08984375"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.7265625"/>
+    <col min="19" max="16384" style="4" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
@@ -960,25 +988,25 @@
   <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.08984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.90625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="4"/>
-    <col min="5" max="5" width="18.36328125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="4"/>
-    <col min="8" max="8" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.54296875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9" style="4" customWidth="1"/>
-    <col min="11" max="11" width="8.54296875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="5.7265625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="8.453125" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9.6328125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="5" style="4" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="5.7265625" style="4" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="8.08984375"/>
+    <col min="2" max="2" customWidth="true" style="4" width="23.90625"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" style="4" width="8.7265625"/>
+    <col min="5" max="5" customWidth="true" style="11" width="18.36328125"/>
+    <col min="6" max="6" customWidth="true" style="4" width="7.36328125"/>
+    <col min="7" max="7" style="4" width="8.7265625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="7.81640625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="6.54296875"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.0"/>
+    <col min="11" max="11" customWidth="true" style="4" width="8.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="5.7265625"/>
+    <col min="13" max="13" customWidth="true" style="4" width="8.453125"/>
+    <col min="14" max="14" customWidth="true" style="4" width="9.6328125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="5.0"/>
+    <col min="16" max="16" customWidth="true" style="4" width="6.1796875"/>
+    <col min="17" max="17" customWidth="true" style="4" width="5.08984375"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.7265625"/>
+    <col min="19" max="16384" style="4" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
@@ -1113,26 +1141,26 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="7.90625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="10" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9.90625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="7.54296875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.453125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="9.6328125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="5" style="4" customWidth="1"/>
-    <col min="17" max="17" width="6.1796875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="4" customWidth="1"/>
-    <col min="19" max="19" width="5.7265625" style="4" customWidth="1"/>
-    <col min="20" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.81640625"/>
+    <col min="2" max="2" customWidth="true" style="4" width="19.54296875"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" customWidth="true" style="4" width="7.90625"/>
+    <col min="5" max="5" customWidth="true" style="4" width="11.0"/>
+    <col min="6" max="6" customWidth="true" style="11" width="11.1796875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.54296875"/>
+    <col min="8" max="8" customWidth="true" style="4" width="9.90625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="10.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.90625"/>
+    <col min="11" max="11" customWidth="true" style="4" width="7.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.54296875"/>
+    <col min="13" max="13" customWidth="true" style="4" width="5.7265625"/>
+    <col min="14" max="14" customWidth="true" style="4" width="8.453125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="9.6328125"/>
+    <col min="16" max="16" customWidth="true" style="4" width="5.0"/>
+    <col min="17" max="17" customWidth="true" style="4" width="6.1796875"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.08984375"/>
+    <col min="19" max="19" customWidth="true" style="4" width="5.7265625"/>
+    <col min="20" max="16384" style="4" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25" x14ac:dyDescent="0.25">
@@ -1279,26 +1307,26 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="7.90625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="10" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9.90625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="7.54296875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" style="4" customWidth="1"/>
-    <col min="13" max="13" width="5.7265625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.453125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="9.6328125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="5" style="4" customWidth="1"/>
-    <col min="17" max="17" width="6.1796875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="5.08984375" style="4" customWidth="1"/>
-    <col min="19" max="19" width="5.7265625" style="4" customWidth="1"/>
-    <col min="20" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.81640625"/>
+    <col min="2" max="2" customWidth="true" style="4" width="19.54296875"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" customWidth="true" style="4" width="7.90625"/>
+    <col min="5" max="5" customWidth="true" style="4" width="11.0"/>
+    <col min="6" max="6" customWidth="true" style="11" width="11.1796875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.54296875"/>
+    <col min="8" max="8" customWidth="true" style="4" width="9.90625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="10.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.90625"/>
+    <col min="11" max="11" customWidth="true" style="4" width="7.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.54296875"/>
+    <col min="13" max="13" customWidth="true" style="4" width="5.7265625"/>
+    <col min="14" max="14" customWidth="true" style="4" width="8.453125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="9.6328125"/>
+    <col min="16" max="16" customWidth="true" style="4" width="5.0"/>
+    <col min="17" max="17" customWidth="true" style="4" width="6.1796875"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.08984375"/>
+    <col min="19" max="19" customWidth="true" style="4" width="5.7265625"/>
+    <col min="20" max="16384" style="4" width="8.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -1388,14 +1416,24 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B2" s="5"/>
+      <c r="A2" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="H2" s="4" t="s">
         <v>54</v>
       </c>
@@ -1405,7 +1443,12 @@
       <c r="E3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="K3" s="12"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
@@ -1430,13 +1473,13 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.7265625" style="7" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">

--- a/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193BA79-F68E-43BD-80F9-FA697F96726A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C446BD7-E466-4399-91B4-B46CAA139C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="5" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
   <si>
     <t>Result</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Thu Sep 10 21:03:31 IST 2026</t>
-  </si>
-  <si>
     <t>CardNo</t>
   </si>
   <si>
@@ -241,9 +238,6 @@
     <t>Checking</t>
   </si>
   <si>
-    <t>Wed Sep 16 22:38:43 IST 2026</t>
-  </si>
-  <si>
     <t>Savings</t>
   </si>
   <si>
@@ -253,22 +247,25 @@
     <t>12345</t>
   </si>
   <si>
+    <t>Thu Sep 17 13:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 14:09:28 IST 2026</t>
+  </si>
+  <si>
+    <t>BusinessName</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Thu Sep 17 13:13:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 13:19:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 13:25:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 13:26:31 IST 2026</t>
+    <t>Thu Sep 17 18:23:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 17 19:48:55 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -870,73 +867,73 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
@@ -944,13 +941,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4">
         <v>12</v>
@@ -965,10 +962,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>36</v>
       </c>
       <c r="G3" s="4">
         <v>2028</v>
@@ -1023,73 +1020,73 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="T1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="25" x14ac:dyDescent="0.25">
@@ -1097,16 +1094,16 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" s="4">
         <v>2030</v>
@@ -1118,10 +1115,10 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E3" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" s="4">
         <v>2028</v>
@@ -1177,76 +1174,76 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>47</v>
-      </c>
       <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="25" x14ac:dyDescent="0.25">
@@ -1254,34 +1251,34 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" s="12"/>
     </row>
@@ -1343,111 +1340,111 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>47</v>
-      </c>
       <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="4">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E3" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K3" s="12"/>
     </row>
@@ -1470,19 +1467,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04532628-18FA-4C04-BD27-113F298023B2}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
-    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.81640625"/>
+    <col min="2" max="2" customWidth="true" style="4" width="19.54296875"/>
+    <col min="3" max="3" customWidth="true" style="4" width="9.36328125"/>
+    <col min="4" max="4" customWidth="true" style="4" width="7.90625"/>
+    <col min="5" max="5" customWidth="true" style="4" width="11.0"/>
+    <col min="6" max="6" customWidth="true" style="11" width="11.1796875"/>
+    <col min="7" max="7" customWidth="true" style="4" width="14.54296875"/>
+    <col min="8" max="8" customWidth="true" style="4" width="13.7265625"/>
+    <col min="9" max="9" customWidth="true" style="4" width="10.0"/>
+    <col min="10" max="10" customWidth="true" style="4" width="9.90625"/>
+    <col min="11" max="11" customWidth="true" style="4" width="7.54296875"/>
+    <col min="12" max="12" customWidth="true" style="4" width="8.54296875"/>
+    <col min="13" max="13" customWidth="true" style="4" width="5.7265625"/>
+    <col min="14" max="14" customWidth="true" style="4" width="8.453125"/>
+    <col min="15" max="15" customWidth="true" style="4" width="9.6328125"/>
+    <col min="16" max="16" customWidth="true" style="4" width="5.0"/>
+    <col min="17" max="17" customWidth="true" style="4" width="6.1796875"/>
+    <col min="18" max="18" customWidth="true" style="4" width="5.08984375"/>
+    <col min="19" max="19" customWidth="true" style="4" width="5.7265625"/>
+    <col min="20" max="16384" style="4" width="8.7265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1496,52 +1506,122 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s" s="4">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
+      <c r="B2" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_E2E.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="65">
   <si>
     <t>Result</t>
   </si>
@@ -266,6 +266,15 @@
   </si>
   <si>
     <t>Thu Sep 17 19:48:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Sep 28 18:04:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 29 19:12:49 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
